--- a/results/Int Task Remove ACC 0.4/Rando_5_permute.xlsx
+++ b/results/Int Task Remove ACC 0.4/Rando_5_permute.xlsx
@@ -440,777 +440,777 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7217737775794422</v>
+        <v>0.7293386729412856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7235483665320174</v>
+        <v>0.7307371324914371</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7263910702591179</v>
+        <v>0.7291879893594209</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7254736390664573</v>
+        <v>0.7301355572684544</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7196375480303917</v>
+        <v>0.6926234591154874</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.713244507293665</v>
+        <v>0.6926234591154874</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7059050577523805</v>
+        <v>0.6977675647794515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7112154949086336</v>
+        <v>0.6933154444875889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6887920392704596</v>
+        <v>0.6852382249474056</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6887920392704596</v>
+        <v>0.6937819840391314</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7019217952210123</v>
+        <v>0.6987754061212308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6897540959854416</v>
+        <v>0.698851327464401</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6822036894295467</v>
+        <v>0.698851327464401</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6415486794902259</v>
+        <v>0.6970164650790799</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6514149767889328</v>
+        <v>0.6842471906205265</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6448567636643929</v>
+        <v>0.6827728097272048</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6404347800889033</v>
+        <v>0.6965197888111645</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6442105629190886</v>
+        <v>0.7128828666971898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6372014581534307</v>
+        <v>0.7119955722209022</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6380586159133453</v>
+        <v>0.6766509994378344</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6396981691944803</v>
+        <v>0.6755371000365118</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6383588239725988</v>
+        <v>0.7572667157354228</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6372930274070253</v>
+        <v>0.7648617478136392</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6378644659136351</v>
+        <v>0.7600491460297774</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6378644659136351</v>
+        <v>0.7666519846766389</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5961413411997891</v>
+        <v>0.7498826406718169</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5781676876445259</v>
+        <v>0.7107477962526152</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5607956093122454</v>
+        <v>0.6509217778344452</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5543735909636216</v>
+        <v>0.6500043466417845</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5781676876445259</v>
+        <v>0.6500043466417845</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5752345737683067</v>
+        <v>0.5806968536109002</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5726631004885625</v>
+        <v>0.6261656244385588</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5769500483926119</v>
+        <v>0.6261656244385588</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5797023419705936</v>
+        <v>0.6489530388821596</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5797023419705936</v>
+        <v>0.641222971132503</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5936034819498456</v>
+        <v>0.5695526436275333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5711788672071958</v>
+        <v>0.5756130213796821</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5589821903597281</v>
+        <v>0.5756130213796821</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5589821903597281</v>
+        <v>0.5727100442198358</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5589821903597281</v>
+        <v>0.5692501173593282</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5691063884043188</v>
+        <v>0.5977675647794514</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5557355387227828</v>
+        <v>0.5877517430033556</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5572545451384261</v>
+        <v>0.5877517430033556</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5572545451384261</v>
+        <v>0.4908766886703333</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5569386891687482</v>
+        <v>0.4576214017050427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5546227984259361</v>
+        <v>0.4791297443595078</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5679623522866233</v>
+        <v>0.4262757393637676</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5745205654111634</v>
+        <v>0.425613890708039</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5858455956927677</v>
+        <v>0.4485363408230801</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5475198061977317</v>
+        <v>0.3980440111969492</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5354761311410804</v>
+        <v>0.4077138402869943</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.546652796049772</v>
+        <v>0.4311932401026967</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5446371133662133</v>
+        <v>0.4367725894973543</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5446371133662133</v>
+        <v>0.4367725894973543</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5431482436669429</v>
+        <v>0.4392090271056582</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5383802674054026</v>
+        <v>0.4273270471233925</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5392675618816902</v>
+        <v>0.4198960283285134</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5349661251716924</v>
+        <v>0.4490608355984167</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5319582490567787</v>
+        <v>0.421804493848053</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5328756802494392</v>
+        <v>0.4649127484105779</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5328455435330663</v>
+        <v>0.4960318058268182</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5231589074281211</v>
+        <v>0.4873987956904495</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4915130370275925</v>
+        <v>0.4870829397207718</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4904750589694402</v>
+        <v>0.4867972204674669</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4932273525474219</v>
+        <v>0.434842680545011</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.535548575170823</v>
+        <v>0.4096344764035307</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5375341211380088</v>
+        <v>0.4390873211356906</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5097254661048873</v>
+        <v>0.4393730403889955</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5056204976035514</v>
+        <v>0.4407257153123497</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5011214335804157</v>
+        <v>0.4440384359044203</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5209432792224727</v>
+        <v>0.4608077799092422</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5253988768277629</v>
+        <v>0.4362637426324422</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5148116165450574</v>
+        <v>0.4420528899372345</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5148116165450574</v>
+        <v>0.446023981871606</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5038493859644039</v>
+        <v>0.4451065506789454</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4985847334349481</v>
+        <v>0.4404289845665239</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4686688264646734</v>
+        <v>0.4399021715822355</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.483919164053852</v>
+        <v>0.4337345766660679</v>
       </c>
     </row>
     <row r="80">
@@ -1220,107 +1220,107 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4844761137545133</v>
+        <v>0.4351486841266438</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4834392948008369</v>
+        <v>0.4266964942885128</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4688797834792839</v>
+        <v>0.4123131668472938</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4652401954250146</v>
+        <v>0.4457226147078767</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4664097318411795</v>
+        <v>0.4799700951045223</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.46732716303384</v>
+        <v>0.471921853176236</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4689064428822292</v>
+        <v>0.4738616145166245</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4652668548279599</v>
+        <v>0.4732600392936418</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4514404770874023</v>
+        <v>0.4553936029023976</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4578926321523991</v>
+        <v>0.4659049418419329</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4977409053765061</v>
+        <v>0.4656939848273224</v>
       </c>
     </row>
   </sheetData>
